--- a/02_clean_data/chini_cleaned_fixed_vs_floating_intercept.xlsx
+++ b/02_clean_data/chini_cleaned_fixed_vs_floating_intercept.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sea/Documents/coding_projects/ww_methane_letter/02_clean_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{85DBF8FD-3C3F-B547-8A8E-F9C10C30AE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CF3819-77B3-B746-956B-8D9231326C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-47020" yWindow="3200" windowWidth="35680" windowHeight="22280" xr2:uid="{FF9E0208-DC04-0C4D-BAC0-966A929C6D25}"/>
   </bookViews>
